--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486337_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486337_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. DEBAUT</t>
+          <t>C. DIAZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7893</v>
+        <v>7.2877</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9154</v>
+        <v>6.7493</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8739</v>
+        <v>0.5384</v>
       </c>
       <c r="G2" t="n">
-        <v>5.8523</v>
+        <v>2.8678</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3765</v>
+        <v>-0.4926</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4758</v>
+        <v>3.3603</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3344</v>
+        <v>2.5149</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8173</v>
+        <v>-1.1188</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5172</v>
+        <v>3.6337</v>
       </c>
       <c r="M2" t="n">
-        <v>1.5178</v>
+        <v>0.3529</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5592</v>
+        <v>0.6262</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9586</v>
+        <v>-0.2733</v>
       </c>
       <c r="P2" t="n">
-        <v>-3.0451</v>
+        <v>1.5225</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.2626</v>
+        <v>-0.2175</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2175</v>
+        <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>4.9821</v>
+        <v>0.4422</v>
       </c>
       <c r="T2" t="n">
-        <v>3.6484</v>
+        <v>-0.2632</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3337</v>
+        <v>0.7054</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>2.4552</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1952</v>
+        <v>4.7151</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1952</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.1131</v>
+        <v>6.4911</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1997</v>
+        <v>4.2249</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9135</v>
+        <v>2.2662</v>
       </c>
       <c r="G3" t="n">
         <v>2.2743</v>
@@ -688,13 +688,13 @@
         <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5789</v>
+        <v>0.9568</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1334</v>
+        <v>-0.1081</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7123</v>
+        <v>1.065</v>
       </c>
       <c r="V3" t="n">
         <v>2.8249</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. DIAZ RODRIGUEZ</t>
+          <t>J. GODSPOWER JOHNSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.4686</v>
+        <v>4.803</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0536</v>
+        <v>3.2908</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4151</v>
+        <v>1.5123</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8678</v>
+        <v>3.7291</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4926</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3603</v>
+        <v>4.3102</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5149</v>
+        <v>4.1038</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.1188</v>
+        <v>-0.5443</v>
       </c>
       <c r="L4" t="n">
-        <v>3.6337</v>
+        <v>4.6481</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3529</v>
+        <v>-0.3747</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6262</v>
+        <v>-0.0368</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2733</v>
+        <v>-0.3379</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5225</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3769</v>
+        <v>0.9217</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9589</v>
+        <v>0.0793</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5821</v>
+        <v>0.8424</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4552</v>
+        <v>0.3698</v>
       </c>
       <c r="W4" t="n">
-        <v>4.7151</v>
+        <v>0.1952</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2599</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GODSPOWER JOHNSON</t>
+          <t>L. DEBAUT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.6552</v>
+        <v>4.5968</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5265</v>
+        <v>2.3702</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1287</v>
+        <v>2.2266</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7291</v>
+        <v>5.8523</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5810999999999999</v>
+        <v>4.3765</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3102</v>
+        <v>1.4758</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1038</v>
+        <v>4.3344</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5443</v>
+        <v>3.8173</v>
       </c>
       <c r="L5" t="n">
-        <v>4.6481</v>
+        <v>0.5172</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3747</v>
+        <v>1.5178</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0368</v>
+        <v>0.5592</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3379</v>
+        <v>0.9586</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2175</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R5" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7739</v>
+        <v>1.7896</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6850000000000001</v>
+        <v>1.1032</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4588</v>
+        <v>0.6865</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0.1952</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1745</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4976</v>
+        <v>3.8668</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2754</v>
+        <v>1.1514</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2222</v>
+        <v>2.7154</v>
       </c>
       <c r="G6" t="n">
         <v>2.2101</v>
@@ -922,13 +922,13 @@
         <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9078000000000001</v>
+        <v>0.4614</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9469</v>
+        <v>-0.0709</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0392</v>
+        <v>0.5323</v>
       </c>
       <c r="V6" t="n">
         <v>0.7602</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6915</v>
+        <v>1.9334</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1189</v>
+        <v>0.2991</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5726</v>
+        <v>1.6343</v>
       </c>
       <c r="G7" t="n">
         <v>0.7326</v>
@@ -1000,13 +1000,13 @@
         <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.281</v>
+        <v>-0.0391</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6044</v>
+        <v>-0.4242</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3235</v>
+        <v>0.3851</v>
       </c>
       <c r="V7" t="n">
         <v>0.3698</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4753</v>
+        <v>0.5062</v>
       </c>
       <c r="E8" t="n">
         <v>0.6182</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1429</v>
+        <v>-0.1121</v>
       </c>
       <c r="G8" t="n">
         <v>0.0883</v>
@@ -1078,13 +1078,13 @@
         <v>0.435</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0479</v>
+        <v>-0.0171</v>
       </c>
       <c r="T8" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5539</v>
+        <v>-1.0701</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5167</v>
+        <v>-2.1561</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9627</v>
+        <v>1.086</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7143</v>
@@ -1156,13 +1156,13 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2519</v>
+        <v>0.2319</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4675</v>
+        <v>-0.1069</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2156</v>
+        <v>0.3389</v>
       </c>
       <c r="V9" t="n">
         <v>0.9347</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7095</v>
+        <v>-2.4446</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6419</v>
+        <v>-1.6851</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0677</v>
+        <v>-0.7594</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9957</v>
@@ -1234,13 +1234,13 @@
         <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1935</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1454</v>
+        <v>-0.1887</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0481</v>
+        <v>0.2602</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9554</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.815</v>
+        <v>-3.9881</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.5002</v>
+        <v>-5.4439</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6852</v>
+        <v>1.4558</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7013</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5688</v>
+        <v>0.2581</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1524</v>
+        <v>-0.0961</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4164</v>
+        <v>0.3542</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9347</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>20.6122</v>
+        <v>21.9822</v>
       </c>
       <c r="E12" t="n">
-        <v>8.0489</v>
+        <v>9.418799999999997</v>
       </c>
       <c r="F12" t="n">
-        <v>12.5633</v>
+        <v>12.5635</v>
       </c>
       <c r="G12" t="n">
         <v>14.3432</v>
       </c>
       <c r="H12" t="n">
-        <v>3.390300000000001</v>
+        <v>3.3903</v>
       </c>
       <c r="I12" t="n">
         <v>10.9528</v>
@@ -1390,16 +1390,16 @@
         <v>9.787699999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>3.7071</v>
+        <v>5.077000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.514</v>
+        <v>-0.1441000000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>5.2212</v>
+        <v>5.2214</v>
       </c>
       <c r="V12" t="n">
-        <v>5.8245</v>
+        <v>5.824499999999999</v>
       </c>
       <c r="W12" t="n">
         <v>11.906</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.754</v>
+        <v>4.1227</v>
       </c>
       <c r="E13" t="n">
-        <v>4.108</v>
+        <v>2.5434</v>
       </c>
       <c r="F13" t="n">
-        <v>1.646</v>
+        <v>1.5792</v>
       </c>
       <c r="G13" t="n">
         <v>2.0407</v>
@@ -1468,13 +1468,13 @@
         <v>1.9576</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9303</v>
+        <v>0.2989</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1993</v>
+        <v>-0.3653</v>
       </c>
       <c r="U13" t="n">
-        <v>0.731</v>
+        <v>0.6642</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1745</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2272</v>
+        <v>0.0294</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1447</v>
+        <v>1.9212</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9174</v>
+        <v>-1.8917</v>
       </c>
       <c r="G14" t="n">
         <v>1.355</v>
@@ -1546,13 +1546,13 @@
         <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4127</v>
+        <v>-0.6105</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5564</v>
+        <v>-0.7799</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1437</v>
+        <v>0.1694</v>
       </c>
       <c r="V14" t="n">
         <v>-2.4552</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.036</v>
+        <v>-0.9049</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1766</v>
+        <v>0.4001</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2126</v>
+        <v>-1.3051</v>
       </c>
       <c r="G15" t="n">
         <v>-0.219</v>
@@ -1624,13 +1624,13 @@
         <v>0.2175</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1422</v>
+        <v>-0.0111</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3425</v>
+        <v>-0.119</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2003</v>
+        <v>0.1078</v>
       </c>
       <c r="V15" t="n">
         <v>0.1952</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.5377</v>
+        <v>-1.2577</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.3744</v>
+        <v>-2.1509</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8367</v>
+        <v>0.8932</v>
       </c>
       <c r="G16" t="n">
         <v>-3.0885</v>
@@ -1702,13 +1702,13 @@
         <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0566</v>
+        <v>-0.7766</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3098</v>
+        <v>-1.0863</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2532</v>
+        <v>0.3097</v>
       </c>
       <c r="V16" t="n">
         <v>2.8249</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8663</v>
+        <v>-1.4077</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4332</v>
+        <v>-0.0979</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4331</v>
+        <v>-1.3098</v>
       </c>
       <c r="G17" t="n">
         <v>-2.1557</v>
@@ -1780,13 +1780,13 @@
         <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5583</v>
+        <v>-0.0997</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.3377</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1146</v>
+        <v>0.2379</v>
       </c>
       <c r="V17" t="n">
         <v>0.1952</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.8539</v>
+        <v>-2.457</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5352</v>
+        <v>-1.1999</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3187</v>
+        <v>-1.2571</v>
       </c>
       <c r="G18" t="n">
         <v>-0.696</v>
@@ -1858,13 +1858,13 @@
         <v>0.2175</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8974</v>
+        <v>-0.5004999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.4182</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.144</v>
+        <v>-0.0823</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3904</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.8239</v>
+        <v>-3.427</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4941</v>
+        <v>-1.1589</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3298</v>
+        <v>-2.2681</v>
       </c>
       <c r="G19" t="n">
         <v>-2.7711</v>
@@ -1936,13 +1936,13 @@
         <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5754</v>
+        <v>-0.1784</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.536</v>
+        <v>-0.2007</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0394</v>
+        <v>0.0222</v>
       </c>
       <c r="V19" t="n">
         <v>-1.13</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CARRALERO MARTIN</t>
+          <t>H. ATENCIA SUAREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.993</v>
+        <v>-3.6705</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2373</v>
+        <v>-4.535</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7556</v>
+        <v>0.8645</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.9064</v>
+        <v>-5.482</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9159</v>
+        <v>-2.536</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9905</v>
+        <v>-2.946</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1347</v>
+        <v>-5.0379</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4806</v>
+        <v>-2.3653</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3459</v>
+        <v>-2.6726</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7716</v>
+        <v>-0.4441</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4353</v>
+        <v>-0.1707</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3364</v>
+        <v>-0.2733</v>
       </c>
       <c r="P20" t="n">
-        <v>1.305</v>
+        <v>2.3926</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>2.3926</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1317</v>
+        <v>-0.9508</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2103</v>
+        <v>-1.1921</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0786</v>
+        <v>0.2412</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.2599</v>
+        <v>0.3698</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1952</v>
+        <v>1.695</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4552</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>H. ATENCIA SUAREZ</t>
+          <t>J. CARRALERO MARTIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.6326</v>
+        <v>-4.0559</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.3173</v>
+        <v>-2.5726</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6847</v>
+        <v>-1.4833</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.482</v>
+        <v>-2.9064</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.536</v>
+        <v>-1.9159</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.946</v>
+        <v>-0.9905</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.0379</v>
+        <v>-1.1347</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.3653</v>
+        <v>-1.4806</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.6726</v>
+        <v>0.3459</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4441</v>
+        <v>-1.7716</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1707</v>
+        <v>-0.4353</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2733</v>
+        <v>-1.3364</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3926</v>
+        <v>1.305</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
         <v>2.3926</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.913</v>
+        <v>-0.1947</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.9744</v>
+        <v>-0.5456</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0614</v>
+        <v>0.3509</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3698</v>
+        <v>-2.2599</v>
       </c>
       <c r="W21" t="n">
-        <v>1.695</v>
+        <v>0.1952</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3252</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.85</v>
+        <v>-6.8385</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.6009</v>
+        <v>-5.7127</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2491</v>
+        <v>-1.1258</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4202</v>
@@ -2170,13 +2170,13 @@
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0498</v>
+        <v>0.0613</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0649</v>
+        <v>-0.1766</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1146</v>
+        <v>0.2379</v>
       </c>
       <c r="V22" t="n">
         <v>-2.9995</v>
@@ -2203,25 +2203,25 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-20.6122</v>
+        <v>-19.8671</v>
       </c>
       <c r="E23" t="n">
-        <v>-12.5631</v>
+        <v>-12.5632</v>
       </c>
       <c r="F23" t="n">
-        <v>-8.0489</v>
+        <v>-7.304</v>
       </c>
       <c r="G23" t="n">
         <v>-14.3432</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.3905</v>
+        <v>-3.390500000000001</v>
       </c>
       <c r="I23" t="n">
         <v>-10.9528</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.6359</v>
+        <v>-3.635899999999999</v>
       </c>
       <c r="K23" t="n">
         <v>-0.2094999999999999</v>
@@ -2239,7 +2239,7 @@
         <v>-7.5265</v>
       </c>
       <c r="P23" t="n">
-        <v>3.2627</v>
+        <v>3.262699999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-9.787700000000001</v>
@@ -2248,16 +2248,16 @@
         <v>13.0505</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.7072</v>
+        <v>-2.9621</v>
       </c>
       <c r="T23" t="n">
         <v>-5.2214</v>
       </c>
       <c r="U23" t="n">
-        <v>1.514</v>
+        <v>2.2589</v>
       </c>
       <c r="V23" t="n">
-        <v>-5.8244</v>
+        <v>-5.824400000000001</v>
       </c>
       <c r="W23" t="n">
         <v>6.0816</v>
